--- a/Datos Tesis Upstream/Computacion Emergente/2425-3/Partic. Emergente 2425-3 Secc. 1.xlsx
+++ b/Datos Tesis Upstream/Computacion Emergente/2425-3/Partic. Emergente 2425-3 Secc. 1.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2" conformance="strict">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr dateCompatibility="0" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nelsoncarrillo/Downloads/tesis-prediccion-participacion/Datos Tesis Upstream/Computacion Emergente/2425-3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{7CD49B63-C1D3-AA49-B629-8E2D0E82EF8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{6388BCB6-0A4F-2F43-8D93-D2D985A9918F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16100" activeTab="1" xr2:uid="{D1799069-8F22-914E-A6F3-C6BDE4CB1B7B}"/>
   </bookViews>
   <sheets>
     <sheet name="Calificaciones" sheetId="1" r:id="rId1"/>
     <sheet name="Estandar" sheetId="2" r:id="rId2"/>
+    <sheet name="Cronograma" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="1281" uniqueCount="224">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="1284" uniqueCount="255">
   <si>
     <t>Nombre</t>
   </si>
@@ -880,6 +881,99 @@
   </si>
   <si>
     <t>carnet</t>
+  </si>
+  <si>
+    <t>20201110027</t>
+  </si>
+  <si>
+    <t>20211110726</t>
+  </si>
+  <si>
+    <t>20211110467</t>
+  </si>
+  <si>
+    <t>20221110130</t>
+  </si>
+  <si>
+    <t>20221110432</t>
+  </si>
+  <si>
+    <t>20191120169</t>
+  </si>
+  <si>
+    <t>Materia:</t>
+  </si>
+  <si>
+    <t>Trimestre:</t>
+  </si>
+  <si>
+    <t>Sección:</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Sesiones por semana:</t>
+  </si>
+  <si>
+    <t>semana</t>
+  </si>
+  <si>
+    <t>dia_sesion</t>
+  </si>
+  <si>
+    <t>dia</t>
+  </si>
+  <si>
+    <t>fecha</t>
+  </si>
+  <si>
+    <t>tema</t>
+  </si>
+  <si>
+    <t>tipo_sesion</t>
+  </si>
+  <si>
+    <t>evaluacion</t>
+  </si>
+  <si>
+    <t>valores admitidos</t>
+  </si>
+  <si>
+    <t>contenido</t>
+  </si>
+  <si>
+    <t>sesión de clase que cubre un tema del catálogo</t>
+  </si>
+  <si>
+    <t>examen parcial, quiz, prueba práctica o debate; sin tema de contenido</t>
+  </si>
+  <si>
+    <t>repaso</t>
+  </si>
+  <si>
+    <t>resolución de ejercicios o revisión de tareas, sin contenido nuevo</t>
+  </si>
+  <si>
+    <t>sin_clase</t>
+  </si>
+  <si>
+    <t>feriado o día no laborable</t>
+  </si>
+  <si>
+    <t>administrativa</t>
+  </si>
+  <si>
+    <t>bienvenida, normas del curso, entrega o revisión de notas</t>
+  </si>
+  <si>
+    <t>código del catálogo de la asignatura (CATALOGO_Temas.xlsx); 0 si no hay contenido nuevo</t>
+  </si>
+  <si>
+    <t>1 = primera sesión de la semana; 2 = segunda sesión, si la sección tiene dos</t>
+  </si>
+  <si>
+    <t>evaluación aplicada o entregada ese día, si hubo alguna</t>
   </si>
 </sst>
 </file>
@@ -978,17 +1072,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Heading" xfId="1" xr:uid="{8FF5187C-26DB-F34D-8784-ADCE6A26267C}"/>
@@ -7226,76 +7320,76 @@
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>209</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3" t="s">
+      <c r="G5" s="4"/>
+      <c r="H5" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3" t="s">
+      <c r="I5" s="4"/>
+      <c r="J5" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3" t="s">
+      <c r="K5" s="4"/>
+      <c r="L5" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3" t="s">
+      <c r="M5" s="4"/>
+      <c r="N5" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3" t="s">
+      <c r="O5" s="4"/>
+      <c r="P5" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3" t="s">
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3" t="s">
+      <c r="S5" s="4"/>
+      <c r="T5" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3" t="s">
+      <c r="U5" s="4"/>
+      <c r="V5" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="W5" s="3"/>
-      <c r="X5" s="3" t="s">
+      <c r="W5" s="4"/>
+      <c r="X5" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="Y5" s="3"/>
-      <c r="Z5" s="3" t="s">
+      <c r="Y5" s="4"/>
+      <c r="Z5" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="AA5" s="3"/>
-      <c r="AB5" s="3" t="s">
+      <c r="AA5" s="4"/>
+      <c r="AB5" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="AC5" s="3"/>
+      <c r="AC5" s="4"/>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="5"/>
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="7"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1" t="s">
         <v>222</v>
@@ -7358,7 +7452,7 @@
       <c r="D7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="3">
         <v>20221110206</v>
       </c>
       <c r="F7" s="1"/>
@@ -7368,13 +7462,7 @@
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
       <c r="X7" s="1"/>
-      <c r="Y7" t="s">
-        <v>55</v>
-      </c>
       <c r="Z7" s="1"/>
-      <c r="AA7" t="s">
-        <v>55</v>
-      </c>
       <c r="AB7" s="1"/>
       <c r="AC7" s="1"/>
     </row>
@@ -7391,7 +7479,7 @@
       <c r="D8" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="3">
         <v>20221110593</v>
       </c>
       <c r="F8" s="1"/>
@@ -7433,7 +7521,7 @@
       <c r="D9" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="3">
         <v>20221110062</v>
       </c>
       <c r="F9" s="1"/>
@@ -7469,7 +7557,7 @@
       <c r="D10" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="3">
         <v>20201110338</v>
       </c>
       <c r="F10" s="1"/>
@@ -7479,13 +7567,7 @@
       <c r="U10" s="1"/>
       <c r="V10" s="1"/>
       <c r="X10" s="1"/>
-      <c r="Y10" t="s">
-        <v>55</v>
-      </c>
       <c r="Z10" s="1"/>
-      <c r="AA10" t="s">
-        <v>55</v>
-      </c>
       <c r="AB10" s="1"/>
       <c r="AC10" s="1"/>
     </row>
@@ -7502,10 +7584,8 @@
       <c r="D11" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>20201110027</t>
-        </is>
+      <c r="E11" s="3" t="s">
+        <v>224</v>
       </c>
       <c r="F11" s="1"/>
       <c r="Q11">
@@ -7540,22 +7620,14 @@
       <c r="D12" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>20211110726</t>
-        </is>
+      <c r="E12" s="3" t="s">
+        <v>225</v>
       </c>
       <c r="F12" s="1"/>
       <c r="U12" s="1"/>
       <c r="V12" s="1"/>
       <c r="X12" s="1"/>
-      <c r="Y12" t="s">
-        <v>55</v>
-      </c>
       <c r="Z12" s="1"/>
-      <c r="AA12" t="s">
-        <v>55</v>
-      </c>
       <c r="AB12" s="1"/>
       <c r="AC12" s="1"/>
     </row>
@@ -7572,22 +7644,14 @@
       <c r="D13" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>20211110467</t>
-        </is>
+      <c r="E13" s="3" t="s">
+        <v>226</v>
       </c>
       <c r="F13" s="1"/>
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
       <c r="X13" s="1"/>
-      <c r="Y13" t="s">
-        <v>55</v>
-      </c>
       <c r="Z13" s="1"/>
-      <c r="AA13" t="s">
-        <v>55</v>
-      </c>
       <c r="AB13" s="1"/>
       <c r="AC13" s="1"/>
     </row>
@@ -7604,10 +7668,8 @@
       <c r="D14" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>20221110130</t>
-        </is>
+      <c r="E14" s="3" t="s">
+        <v>227</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14">
@@ -7645,22 +7707,14 @@
       <c r="D15" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>20221110432</t>
-        </is>
+      <c r="E15" s="3" t="s">
+        <v>228</v>
       </c>
       <c r="F15" s="1"/>
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
       <c r="X15" s="1"/>
-      <c r="Y15" t="s">
-        <v>55</v>
-      </c>
       <c r="Z15" s="1"/>
-      <c r="AA15" t="s">
-        <v>55</v>
-      </c>
       <c r="AB15" s="1"/>
       <c r="AC15" s="1"/>
     </row>
@@ -7677,7 +7731,7 @@
       <c r="D16" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="3">
         <v>20221110386</v>
       </c>
       <c r="F16" s="1"/>
@@ -7707,20 +7761,14 @@
       <c r="D17" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="3">
         <v>20221110121</v>
       </c>
       <c r="F17" s="1"/>
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
       <c r="X17" s="1"/>
-      <c r="Y17" t="s">
-        <v>55</v>
-      </c>
       <c r="Z17" s="1"/>
-      <c r="AA17" t="s">
-        <v>55</v>
-      </c>
       <c r="AB17" s="1"/>
       <c r="AC17" s="1"/>
     </row>
@@ -7737,7 +7785,7 @@
       <c r="D18" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="3">
         <v>20221110087</v>
       </c>
       <c r="F18" s="1"/>
@@ -7747,13 +7795,7 @@
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
       <c r="X18" s="1"/>
-      <c r="Y18" t="s">
-        <v>55</v>
-      </c>
       <c r="Z18" s="1"/>
-      <c r="AA18" t="s">
-        <v>55</v>
-      </c>
       <c r="AB18" s="1"/>
       <c r="AC18" s="1"/>
     </row>
@@ -7770,7 +7812,7 @@
       <c r="D19" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="3">
         <v>20211110786</v>
       </c>
       <c r="F19" s="1"/>
@@ -7780,13 +7822,7 @@
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
       <c r="X19" s="1"/>
-      <c r="Y19" t="s">
-        <v>55</v>
-      </c>
       <c r="Z19" s="1"/>
-      <c r="AA19" t="s">
-        <v>55</v>
-      </c>
       <c r="AB19" s="1"/>
       <c r="AC19" s="1"/>
     </row>
@@ -7803,20 +7839,14 @@
       <c r="D20" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="3">
         <v>20211110515</v>
       </c>
       <c r="F20" s="1"/>
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
       <c r="X20" s="1"/>
-      <c r="Y20" t="s">
-        <v>55</v>
-      </c>
       <c r="Z20" s="1"/>
-      <c r="AA20" t="s">
-        <v>55</v>
-      </c>
       <c r="AB20" s="1"/>
       <c r="AC20" s="1"/>
     </row>
@@ -7833,20 +7863,14 @@
       <c r="D21" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="3">
         <v>20231110834</v>
       </c>
       <c r="F21" s="1"/>
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
       <c r="X21" s="1"/>
-      <c r="Y21" t="s">
-        <v>55</v>
-      </c>
       <c r="Z21" s="1"/>
-      <c r="AA21" t="s">
-        <v>55</v>
-      </c>
       <c r="AB21" s="1"/>
       <c r="AC21" s="1"/>
     </row>
@@ -7863,20 +7887,14 @@
       <c r="D22" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E22" s="7">
+      <c r="E22" s="3">
         <v>20231110138</v>
       </c>
       <c r="F22" s="1"/>
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
       <c r="X22" s="1"/>
-      <c r="Y22" t="s">
-        <v>55</v>
-      </c>
       <c r="Z22" s="1"/>
-      <c r="AA22" t="s">
-        <v>55</v>
-      </c>
       <c r="AB22" s="1"/>
       <c r="AC22" s="1"/>
     </row>
@@ -7893,7 +7911,7 @@
       <c r="D23" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="3">
         <v>20221110080</v>
       </c>
       <c r="F23" s="1"/>
@@ -7916,9 +7934,6 @@
         <v>1</v>
       </c>
       <c r="Z23" s="1"/>
-      <c r="AA23" t="s">
-        <v>55</v>
-      </c>
       <c r="AB23" s="1"/>
       <c r="AC23" s="1"/>
     </row>
@@ -7935,7 +7950,7 @@
       <c r="D24" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="3">
         <v>20221110395</v>
       </c>
       <c r="K24">
@@ -7970,7 +7985,7 @@
       <c r="D25" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="3">
         <v>20221110357</v>
       </c>
       <c r="S25">
@@ -7978,9 +7993,6 @@
       </c>
       <c r="Y25">
         <v>1</v>
-      </c>
-      <c r="AA25" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.25">
@@ -7996,14 +8008,8 @@
       <c r="D26" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E26" s="3">
         <v>20231110482</v>
-      </c>
-      <c r="Y26" t="s">
-        <v>55</v>
-      </c>
-      <c r="AA26" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.25">
@@ -8019,7 +8025,7 @@
       <c r="D27" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E27" s="7">
+      <c r="E27" s="3">
         <v>20231110383</v>
       </c>
       <c r="G27">
@@ -8051,14 +8057,8 @@
       <c r="D28" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E28" s="7">
+      <c r="E28" s="3">
         <v>20221110543</v>
-      </c>
-      <c r="Y28" t="s">
-        <v>55</v>
-      </c>
-      <c r="AA28" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.25">
@@ -8074,14 +8074,8 @@
       <c r="D29" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E29" s="7">
+      <c r="E29" s="3">
         <v>20231110518</v>
-      </c>
-      <c r="Y29" t="s">
-        <v>55</v>
-      </c>
-      <c r="AA29" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:29" x14ac:dyDescent="0.25">
@@ -8097,7 +8091,7 @@
       <c r="D30" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E30" s="3">
         <v>20221110488</v>
       </c>
       <c r="K30">
@@ -8108,12 +8102,6 @@
       </c>
       <c r="W30">
         <v>1</v>
-      </c>
-      <c r="Y30" t="s">
-        <v>55</v>
-      </c>
-      <c r="AA30" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:29" x14ac:dyDescent="0.25">
@@ -8129,14 +8117,8 @@
       <c r="D31" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="E31" s="7">
+      <c r="E31" s="3">
         <v>20221110058</v>
-      </c>
-      <c r="Y31" t="s">
-        <v>55</v>
-      </c>
-      <c r="AA31" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.25">
@@ -8152,7 +8134,7 @@
       <c r="D32" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E32" s="7">
+      <c r="E32" s="3">
         <v>20221110420</v>
       </c>
       <c r="G32">
@@ -8172,9 +8154,6 @@
       </c>
       <c r="Y32">
         <v>1</v>
-      </c>
-      <c r="AA32" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.25">
@@ -8190,7 +8169,7 @@
       <c r="D33" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E33" s="7">
+      <c r="E33" s="3">
         <v>20231110297</v>
       </c>
       <c r="K33">
@@ -8225,14 +8204,8 @@
       <c r="D34" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="E34" s="7">
+      <c r="E34" s="3">
         <v>20201110236</v>
-      </c>
-      <c r="Y34" t="s">
-        <v>55</v>
-      </c>
-      <c r="AA34" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.25">
@@ -8248,7 +8221,7 @@
       <c r="D35" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="E35" s="7">
+      <c r="E35" s="3">
         <v>20221110586</v>
       </c>
       <c r="G35">
@@ -8268,9 +8241,6 @@
       </c>
       <c r="Y35">
         <v>1</v>
-      </c>
-      <c r="AA35" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.25">
@@ -8286,7 +8256,7 @@
       <c r="D36" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E36" s="7">
+      <c r="E36" s="3">
         <v>20201110220</v>
       </c>
       <c r="W36">
@@ -8312,7 +8282,7 @@
       <c r="D37" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="E37" s="7">
+      <c r="E37" s="3">
         <v>20231110532</v>
       </c>
       <c r="Q37">
@@ -8323,9 +8293,6 @@
       </c>
       <c r="Y37">
         <v>1</v>
-      </c>
-      <c r="AA37" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.25">
@@ -8341,14 +8308,8 @@
       <c r="D38" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="E38" s="7">
+      <c r="E38" s="3">
         <v>20221110207</v>
-      </c>
-      <c r="Y38" t="s">
-        <v>55</v>
-      </c>
-      <c r="AA38" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.25">
@@ -8364,14 +8325,8 @@
       <c r="D39" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="E39" s="7">
+      <c r="E39" s="3">
         <v>20221110251</v>
-      </c>
-      <c r="Y39" t="s">
-        <v>55</v>
-      </c>
-      <c r="AA39" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.25">
@@ -8387,7 +8342,7 @@
       <c r="D40" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E40" s="7">
+      <c r="E40" s="3">
         <v>20221110600</v>
       </c>
       <c r="W40">
@@ -8413,7 +8368,7 @@
       <c r="D41" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E41" s="7">
+      <c r="E41" s="3">
         <v>20221110023</v>
       </c>
       <c r="S41">
@@ -8442,7 +8397,7 @@
       <c r="D42" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="E42" s="7">
+      <c r="E42" s="3">
         <v>20221110261</v>
       </c>
       <c r="G42">
@@ -8480,17 +8435,11 @@
       <c r="D43" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E43" s="7">
+      <c r="E43" s="3">
         <v>20211110017</v>
       </c>
       <c r="Q43">
         <v>1</v>
-      </c>
-      <c r="Y43" t="s">
-        <v>55</v>
-      </c>
-      <c r="AA43" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="44" spans="1:27" x14ac:dyDescent="0.25">
@@ -8506,20 +8455,19 @@
       <c r="D44" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="E44" s="1" t="inlineStr">
-        <is>
-          <t>20191120169</t>
-        </is>
-      </c>
-      <c r="Y44" t="s">
-        <v>55</v>
-      </c>
-      <c r="AA44" t="s">
-        <v>55</v>
+      <c r="E44" s="1" t="s">
+        <v>229</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="E5:E6"/>
     <mergeCell ref="V5:W5"/>
     <mergeCell ref="X5:Y5"/>
     <mergeCell ref="Z5:AA5"/>
@@ -8530,14 +8478,206 @@
     <mergeCell ref="P5:Q5"/>
     <mergeCell ref="R5:S5"/>
     <mergeCell ref="T5:U5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <pageMargins left="0.70000000000000007" right="0.70000000000000007" top="0.75" bottom="0.75" header="0.30000000000000004" footer="0.30000000000000004"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">semana</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dia_sesion</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tema</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tipo_sesion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sin_clase</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nota:</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tema = código del catálogo de la asignatura. Si la sesión no cubre contenido nuevo: tema = 0 y tipo_sesion indica la causa (evaluacion, repaso, sin_clase, administrativa). Si tema &gt; 0 la sesión es de contenido y tipo_sesion queda vacío.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/Datos Tesis Upstream/Computacion Emergente/2425-3/Partic. Emergente 2425-3 Secc. 1.xlsx
+++ b/Datos Tesis Upstream/Computacion Emergente/2425-3/Partic. Emergente 2425-3 Secc. 1.xlsx
@@ -8522,7 +8522,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -8549,7 +8549,7 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -8576,7 +8576,7 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -8587,7 +8587,7 @@
         <v>1</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -8598,7 +8598,7 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -8625,7 +8625,7 @@
         <v>1</v>
       </c>
       <c r="C10">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -8636,7 +8636,7 @@
         <v>1</v>
       </c>
       <c r="C11">
-        <v>28</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -8647,7 +8647,7 @@
         <v>1</v>
       </c>
       <c r="C12">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
